--- a/data/2026-2027/Pré-séance.xlsx
+++ b/data/2026-2027/Pré-séance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4968B66-0F4B-B040-8767-BE41F1B5C8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB9DF85-7F58-994E-B45C-C4A46F560A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="144">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -448,6 +448,27 @@
   <si>
     <t>Cheville droite </t>
   </si>
+  <si>
+    <t>Cerveaux </t>
+  </si>
+  <si>
+    <t>mollet droit</t>
+  </si>
+  <si>
+    <t>9h20</t>
+  </si>
+  <si>
+    <t>Adducteurs </t>
+  </si>
+  <si>
+    <t>Cervicale/trapeze</t>
+  </si>
+  <si>
+    <t>9h 30</t>
+  </si>
+  <si>
+    <t>Bassin </t>
+  </si>
 </sst>
 </file>
 
@@ -842,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:T597"/>
+  <dimension ref="A1:T635"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -19092,6 +19113,1174 @@
         <v>6</v>
       </c>
     </row>
+    <row r="598" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A598" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C598" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D598" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E598" s="1">
+        <v>7</v>
+      </c>
+      <c r="F598" s="1">
+        <v>7</v>
+      </c>
+      <c r="G598" s="1">
+        <v>3</v>
+      </c>
+      <c r="H598" s="1">
+        <v>0</v>
+      </c>
+      <c r="I598" s="2"/>
+      <c r="J598" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="599" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A599" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C599" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D599" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E599" s="1">
+        <v>8</v>
+      </c>
+      <c r="F599" s="1">
+        <v>1</v>
+      </c>
+      <c r="G599" s="1">
+        <v>0</v>
+      </c>
+      <c r="H599" s="1">
+        <v>3</v>
+      </c>
+      <c r="I599" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J599" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="600" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A600" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C600" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D600" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E600" s="1">
+        <v>7</v>
+      </c>
+      <c r="F600" s="1">
+        <v>5</v>
+      </c>
+      <c r="G600" s="1">
+        <v>5</v>
+      </c>
+      <c r="H600" s="1">
+        <v>6</v>
+      </c>
+      <c r="I600" s="2"/>
+      <c r="J600" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="601" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A601" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C601" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D601" s="5">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E601" s="1">
+        <v>9</v>
+      </c>
+      <c r="F601" s="1">
+        <v>1</v>
+      </c>
+      <c r="G601" s="1">
+        <v>0</v>
+      </c>
+      <c r="H601" s="1">
+        <v>0</v>
+      </c>
+      <c r="I601" s="2"/>
+      <c r="J601" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="602" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A602" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C602" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D602" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E602" s="1">
+        <v>8</v>
+      </c>
+      <c r="F602" s="1">
+        <v>2</v>
+      </c>
+      <c r="G602" s="1">
+        <v>0</v>
+      </c>
+      <c r="H602" s="1">
+        <v>3</v>
+      </c>
+      <c r="I602" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J602" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="603" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A603" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C603" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D603" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E603" s="1">
+        <v>8</v>
+      </c>
+      <c r="F603" s="1">
+        <v>2</v>
+      </c>
+      <c r="G603" s="1">
+        <v>2</v>
+      </c>
+      <c r="H603" s="1">
+        <v>0</v>
+      </c>
+      <c r="I603" s="2"/>
+      <c r="J603" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="604" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A604" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C604" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D604" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E604" s="1">
+        <v>6</v>
+      </c>
+      <c r="F604" s="1">
+        <v>6</v>
+      </c>
+      <c r="G604" s="1">
+        <v>0</v>
+      </c>
+      <c r="H604" s="1">
+        <v>5</v>
+      </c>
+      <c r="I604" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J604" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="605" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A605" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C605" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D605" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E605" s="1">
+        <v>5</v>
+      </c>
+      <c r="F605" s="1">
+        <v>3</v>
+      </c>
+      <c r="G605" s="1">
+        <v>1</v>
+      </c>
+      <c r="H605" s="1">
+        <v>0</v>
+      </c>
+      <c r="I605" s="2"/>
+      <c r="J605" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="606" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A606" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D606" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E606" s="1">
+        <v>5</v>
+      </c>
+      <c r="F606" s="1">
+        <v>3</v>
+      </c>
+      <c r="G606" s="1">
+        <v>3</v>
+      </c>
+      <c r="H606" s="1">
+        <v>1</v>
+      </c>
+      <c r="I606" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J606" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="607" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A607" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C607" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D607" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E607" s="1">
+        <v>9</v>
+      </c>
+      <c r="F607" s="1">
+        <v>2</v>
+      </c>
+      <c r="G607" s="1">
+        <v>3</v>
+      </c>
+      <c r="H607" s="1">
+        <v>3</v>
+      </c>
+      <c r="I607" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J607" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="608" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A608" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C608" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D608" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E608" s="1">
+        <v>10</v>
+      </c>
+      <c r="F608" s="1">
+        <v>0</v>
+      </c>
+      <c r="G608" s="1">
+        <v>0</v>
+      </c>
+      <c r="H608" s="1">
+        <v>0</v>
+      </c>
+      <c r="I608" s="2"/>
+      <c r="J608" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="609" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A609" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C609" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D609" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E609" s="1">
+        <v>8</v>
+      </c>
+      <c r="F609" s="1">
+        <v>2</v>
+      </c>
+      <c r="G609" s="1">
+        <v>0</v>
+      </c>
+      <c r="H609" s="1">
+        <v>0</v>
+      </c>
+      <c r="I609" s="2"/>
+      <c r="J609" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="610" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A610" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C610" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D610" s="1">
+        <v>10</v>
+      </c>
+      <c r="E610" s="1">
+        <v>7</v>
+      </c>
+      <c r="F610" s="1">
+        <v>3</v>
+      </c>
+      <c r="G610" s="1">
+        <v>0</v>
+      </c>
+      <c r="H610" s="1">
+        <v>2</v>
+      </c>
+      <c r="I610" s="2"/>
+      <c r="J610" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="611" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A611" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C611" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D611" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E611" s="1">
+        <v>7</v>
+      </c>
+      <c r="F611" s="1">
+        <v>4</v>
+      </c>
+      <c r="G611" s="1">
+        <v>4</v>
+      </c>
+      <c r="H611" s="1">
+        <v>4</v>
+      </c>
+      <c r="I611" s="2"/>
+      <c r="J611" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="612" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A612" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C612" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D612" s="1">
+        <v>14</v>
+      </c>
+      <c r="E612" s="1">
+        <v>8</v>
+      </c>
+      <c r="F612" s="1">
+        <v>7</v>
+      </c>
+      <c r="G612" s="1">
+        <v>6</v>
+      </c>
+      <c r="H612" s="1">
+        <v>10</v>
+      </c>
+      <c r="I612" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J612" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="613" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A613" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C613" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D613" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E613" s="1">
+        <v>8</v>
+      </c>
+      <c r="F613" s="1">
+        <v>4</v>
+      </c>
+      <c r="G613" s="1">
+        <v>4</v>
+      </c>
+      <c r="H613" s="1">
+        <v>0</v>
+      </c>
+      <c r="I613" s="2"/>
+      <c r="J613" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="614" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A614" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C614" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D614" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E614" s="1">
+        <v>8</v>
+      </c>
+      <c r="F614" s="1">
+        <v>2</v>
+      </c>
+      <c r="G614" s="1">
+        <v>0</v>
+      </c>
+      <c r="H614" s="1">
+        <v>0</v>
+      </c>
+      <c r="I614" s="2"/>
+      <c r="J614" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="615" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A615" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C615" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D615" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E615" s="1">
+        <v>7</v>
+      </c>
+      <c r="F615" s="1">
+        <v>4</v>
+      </c>
+      <c r="G615" s="1">
+        <v>3</v>
+      </c>
+      <c r="H615" s="1">
+        <v>3</v>
+      </c>
+      <c r="I615" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J615" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="616" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A616" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D616" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E616" s="1">
+        <v>5</v>
+      </c>
+      <c r="F616" s="1">
+        <v>4</v>
+      </c>
+      <c r="G616" s="1">
+        <v>0</v>
+      </c>
+      <c r="H616" s="1">
+        <v>0</v>
+      </c>
+      <c r="I616" s="2"/>
+      <c r="J616" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="617" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A617" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C617" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D617" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E617" s="1">
+        <v>7</v>
+      </c>
+      <c r="F617" s="1">
+        <v>4</v>
+      </c>
+      <c r="G617" s="1">
+        <v>0</v>
+      </c>
+      <c r="H617" s="1">
+        <v>0</v>
+      </c>
+      <c r="I617" s="2"/>
+      <c r="J617" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="618" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A618" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C618" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D618" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E618" s="1">
+        <v>4</v>
+      </c>
+      <c r="F618" s="1">
+        <v>7</v>
+      </c>
+      <c r="G618" s="1">
+        <v>6</v>
+      </c>
+      <c r="H618" s="1">
+        <v>6</v>
+      </c>
+      <c r="I618" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J618" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="619" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A619" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C619" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D619" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E619" s="1">
+        <v>5</v>
+      </c>
+      <c r="F619" s="1">
+        <v>4</v>
+      </c>
+      <c r="G619" s="1">
+        <v>3</v>
+      </c>
+      <c r="H619" s="1">
+        <v>1</v>
+      </c>
+      <c r="I619" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J619" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="620" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A620" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C620" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D620" s="1">
+        <v>9</v>
+      </c>
+      <c r="E620" s="1">
+        <v>6</v>
+      </c>
+      <c r="F620" s="1">
+        <v>2</v>
+      </c>
+      <c r="G620" s="1">
+        <v>0</v>
+      </c>
+      <c r="H620" s="1">
+        <v>0</v>
+      </c>
+      <c r="I620" s="2"/>
+      <c r="J620" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="621" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A621" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C621" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D621" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E621" s="1">
+        <v>6</v>
+      </c>
+      <c r="F621" s="1">
+        <v>6</v>
+      </c>
+      <c r="G621" s="1">
+        <v>0</v>
+      </c>
+      <c r="H621" s="1">
+        <v>0</v>
+      </c>
+      <c r="I621" s="2"/>
+      <c r="J621" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="622" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A622" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C622" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D622" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E622" s="1">
+        <v>8</v>
+      </c>
+      <c r="F622" s="1">
+        <v>3</v>
+      </c>
+      <c r="G622" s="1">
+        <v>0</v>
+      </c>
+      <c r="H622" s="1">
+        <v>3</v>
+      </c>
+      <c r="I622" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J622" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="623" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A623" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C623" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D623" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E623" s="1">
+        <v>5</v>
+      </c>
+      <c r="F623" s="1">
+        <v>4</v>
+      </c>
+      <c r="G623" s="1">
+        <v>3</v>
+      </c>
+      <c r="H623" s="1">
+        <v>4</v>
+      </c>
+      <c r="I623" s="2"/>
+      <c r="J623" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="624" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A624" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C624" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D624" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E624" s="1">
+        <v>5</v>
+      </c>
+      <c r="F624" s="1">
+        <v>5</v>
+      </c>
+      <c r="G624" s="1">
+        <v>0</v>
+      </c>
+      <c r="H624" s="1">
+        <v>0</v>
+      </c>
+      <c r="I624" s="2"/>
+      <c r="J624" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="625" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A625" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C625" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D625" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E625" s="1">
+        <v>7</v>
+      </c>
+      <c r="F625" s="1">
+        <v>5</v>
+      </c>
+      <c r="G625" s="1">
+        <v>1</v>
+      </c>
+      <c r="H625" s="1">
+        <v>0</v>
+      </c>
+      <c r="I625" s="2"/>
+      <c r="J625" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="626" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A626" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C626" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D626" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E626" s="1">
+        <v>6</v>
+      </c>
+      <c r="F626" s="1">
+        <v>5</v>
+      </c>
+      <c r="G626" s="1">
+        <v>0</v>
+      </c>
+      <c r="H626" s="1">
+        <v>0</v>
+      </c>
+      <c r="I626" s="2"/>
+      <c r="J626" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="627" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A627" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C627" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D627" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E627" s="1">
+        <v>7</v>
+      </c>
+      <c r="F627" s="1">
+        <v>5</v>
+      </c>
+      <c r="G627" s="1">
+        <v>0</v>
+      </c>
+      <c r="H627" s="1">
+        <v>0</v>
+      </c>
+      <c r="I627" s="2"/>
+      <c r="J627" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="628" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A628" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C628" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D628" s="1">
+        <v>9</v>
+      </c>
+      <c r="E628" s="1">
+        <v>6</v>
+      </c>
+      <c r="F628" s="1">
+        <v>6</v>
+      </c>
+      <c r="G628" s="1">
+        <v>0</v>
+      </c>
+      <c r="H628" s="1">
+        <v>7</v>
+      </c>
+      <c r="I628" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J628" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="629" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A629" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C629" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D629" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E629" s="1">
+        <v>4</v>
+      </c>
+      <c r="F629" s="1">
+        <v>6</v>
+      </c>
+      <c r="G629" s="1">
+        <v>0</v>
+      </c>
+      <c r="H629" s="1">
+        <v>3</v>
+      </c>
+      <c r="I629" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J629" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="630" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A630" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C630" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D630" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E630" s="1">
+        <v>6</v>
+      </c>
+      <c r="F630" s="1">
+        <v>5</v>
+      </c>
+      <c r="G630" s="1">
+        <v>7</v>
+      </c>
+      <c r="H630" s="1">
+        <v>5</v>
+      </c>
+      <c r="I630" s="2"/>
+      <c r="J630" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="631" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A631" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C631" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D631" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E631" s="1">
+        <v>6</v>
+      </c>
+      <c r="F631" s="1">
+        <v>3</v>
+      </c>
+      <c r="G631" s="1">
+        <v>0</v>
+      </c>
+      <c r="H631" s="1">
+        <v>2</v>
+      </c>
+      <c r="I631" s="2"/>
+      <c r="J631" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="632" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A632" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C632" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D632" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E632" s="1">
+        <v>2</v>
+      </c>
+      <c r="F632" s="1">
+        <v>4</v>
+      </c>
+      <c r="G632" s="1">
+        <v>2</v>
+      </c>
+      <c r="H632" s="1">
+        <v>0</v>
+      </c>
+      <c r="I632" s="2"/>
+      <c r="J632" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="633" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A633" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C633" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D633" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E633" s="1">
+        <v>4</v>
+      </c>
+      <c r="F633" s="1">
+        <v>6</v>
+      </c>
+      <c r="G633" s="1">
+        <v>4</v>
+      </c>
+      <c r="H633" s="1">
+        <v>0</v>
+      </c>
+      <c r="I633" s="2"/>
+      <c r="J633" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="634" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A634" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C634" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D634" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E634" s="1">
+        <v>8</v>
+      </c>
+      <c r="F634" s="1">
+        <v>4</v>
+      </c>
+      <c r="G634" s="1">
+        <v>2</v>
+      </c>
+      <c r="H634" s="1">
+        <v>3</v>
+      </c>
+      <c r="I634" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J634" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="635" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A635" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C635" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D635" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E635" s="1">
+        <v>7</v>
+      </c>
+      <c r="F635" s="1">
+        <v>5</v>
+      </c>
+      <c r="G635" s="1">
+        <v>5</v>
+      </c>
+      <c r="H635" s="1">
+        <v>5</v>
+      </c>
+      <c r="I635" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J635" s="1">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Pré-séance.xlsx
+++ b/data/2026-2027/Pré-séance.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB9DF85-7F58-994E-B45C-C4A46F560A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDB542D-8501-4945-8BD2-F97234F81AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="148">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -469,6 +468,18 @@
   <si>
     <t>Bassin </t>
   </si>
+  <si>
+    <t>Nuit blanche </t>
+  </si>
+  <si>
+    <t>8h 20</t>
+  </si>
+  <si>
+    <t>Cheville et genou</t>
+  </si>
+  <si>
+    <t>8h2</t>
+  </si>
 </sst>
 </file>
 
@@ -863,7 +874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:T635"/>
+  <dimension ref="A1:T667"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -20281,6 +20292,980 @@
         <v>7</v>
       </c>
     </row>
+    <row r="636" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A636" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C636" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D636" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E636" s="1">
+        <v>8</v>
+      </c>
+      <c r="F636" s="1">
+        <v>3</v>
+      </c>
+      <c r="G636" s="1">
+        <v>2</v>
+      </c>
+      <c r="H636" s="1">
+        <v>2</v>
+      </c>
+      <c r="I636" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J636" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="637" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A637" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C637" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D637" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E637" s="1">
+        <v>7</v>
+      </c>
+      <c r="F637" s="1">
+        <v>2</v>
+      </c>
+      <c r="G637" s="1">
+        <v>1</v>
+      </c>
+      <c r="H637" s="1">
+        <v>0</v>
+      </c>
+      <c r="I637" s="2"/>
+      <c r="J637" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="638" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A638" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C638" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D638" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E638" s="1">
+        <v>10</v>
+      </c>
+      <c r="F638" s="1">
+        <v>0</v>
+      </c>
+      <c r="G638" s="1">
+        <v>0</v>
+      </c>
+      <c r="H638" s="1">
+        <v>0</v>
+      </c>
+      <c r="I638" s="2"/>
+      <c r="J638" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="639" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A639" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C639" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D639" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E639" s="1">
+        <v>7</v>
+      </c>
+      <c r="F639" s="1">
+        <v>2</v>
+      </c>
+      <c r="G639" s="1">
+        <v>0</v>
+      </c>
+      <c r="H639" s="1">
+        <v>0</v>
+      </c>
+      <c r="I639" s="2"/>
+      <c r="J639" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="640" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A640" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C640" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D640" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="E640" s="1">
+        <v>8</v>
+      </c>
+      <c r="F640" s="1">
+        <v>2</v>
+      </c>
+      <c r="G640" s="1">
+        <v>0</v>
+      </c>
+      <c r="H640" s="1">
+        <v>0</v>
+      </c>
+      <c r="I640" s="2"/>
+      <c r="J640" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="641" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A641" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C641" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D641" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E641" s="1">
+        <v>5</v>
+      </c>
+      <c r="F641" s="1">
+        <v>6</v>
+      </c>
+      <c r="G641" s="1">
+        <v>5</v>
+      </c>
+      <c r="H641" s="1">
+        <v>5</v>
+      </c>
+      <c r="I641" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J641" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="642" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A642" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C642" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D642" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E642" s="1">
+        <v>4</v>
+      </c>
+      <c r="F642" s="1">
+        <v>3</v>
+      </c>
+      <c r="G642" s="1">
+        <v>1</v>
+      </c>
+      <c r="H642" s="1">
+        <v>1</v>
+      </c>
+      <c r="I642" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J642" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="643" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A643" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C643" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D643" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E643" s="1">
+        <v>4</v>
+      </c>
+      <c r="F643" s="1">
+        <v>5</v>
+      </c>
+      <c r="G643" s="1">
+        <v>5</v>
+      </c>
+      <c r="H643" s="1">
+        <v>5</v>
+      </c>
+      <c r="I643" s="2"/>
+      <c r="J643" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="644" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A644" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C644" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D644" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E644" s="1">
+        <v>5</v>
+      </c>
+      <c r="F644" s="1">
+        <v>4</v>
+      </c>
+      <c r="G644" s="1">
+        <v>2</v>
+      </c>
+      <c r="H644" s="1">
+        <v>0</v>
+      </c>
+      <c r="I644" s="2"/>
+      <c r="J644" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="645" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A645" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C645" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D645" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E645" s="1">
+        <v>8</v>
+      </c>
+      <c r="F645" s="1">
+        <v>4</v>
+      </c>
+      <c r="G645" s="1">
+        <v>0</v>
+      </c>
+      <c r="H645" s="1">
+        <v>0</v>
+      </c>
+      <c r="I645" s="2"/>
+      <c r="J645" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="646" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A646" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C646" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D646" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E646" s="1">
+        <v>0</v>
+      </c>
+      <c r="F646" s="1">
+        <v>8</v>
+      </c>
+      <c r="G646" s="1">
+        <v>0</v>
+      </c>
+      <c r="H646" s="1">
+        <v>0</v>
+      </c>
+      <c r="I646" s="2"/>
+      <c r="J646" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="647" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A647" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C647" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D647" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E647" s="1">
+        <v>7</v>
+      </c>
+      <c r="F647" s="1">
+        <v>3</v>
+      </c>
+      <c r="G647" s="1">
+        <v>0</v>
+      </c>
+      <c r="H647" s="1">
+        <v>3</v>
+      </c>
+      <c r="I647" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J647" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="648" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A648" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C648" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D648" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E648" s="1">
+        <v>5</v>
+      </c>
+      <c r="F648" s="1">
+        <v>6</v>
+      </c>
+      <c r="G648" s="1">
+        <v>0</v>
+      </c>
+      <c r="H648" s="1">
+        <v>4</v>
+      </c>
+      <c r="I648" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J648" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="649" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A649" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C649" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D649" s="5">
+        <v>0.40625</v>
+      </c>
+      <c r="E649" s="1">
+        <v>3</v>
+      </c>
+      <c r="F649" s="1">
+        <v>8</v>
+      </c>
+      <c r="G649" s="1">
+        <v>0</v>
+      </c>
+      <c r="H649" s="1">
+        <v>2</v>
+      </c>
+      <c r="I649" s="2"/>
+      <c r="J649" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="650" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A650" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C650" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D650" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E650" s="1">
+        <v>5</v>
+      </c>
+      <c r="F650" s="1">
+        <v>3</v>
+      </c>
+      <c r="G650" s="1">
+        <v>0</v>
+      </c>
+      <c r="H650" s="1">
+        <v>0</v>
+      </c>
+      <c r="I650" s="2"/>
+      <c r="J650" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="651" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A651" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C651" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D651" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E651" s="1">
+        <v>4</v>
+      </c>
+      <c r="F651" s="1">
+        <v>4</v>
+      </c>
+      <c r="G651" s="1">
+        <v>0</v>
+      </c>
+      <c r="H651" s="1">
+        <v>0</v>
+      </c>
+      <c r="I651" s="2"/>
+      <c r="J651" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="652" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A652" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C652" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D652" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E652" s="1">
+        <v>7</v>
+      </c>
+      <c r="F652" s="1">
+        <v>3</v>
+      </c>
+      <c r="G652" s="1">
+        <v>0</v>
+      </c>
+      <c r="H652" s="1">
+        <v>0</v>
+      </c>
+      <c r="I652" s="2"/>
+      <c r="J652" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="653" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A653" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C653" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D653" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E653" s="1">
+        <v>8</v>
+      </c>
+      <c r="F653" s="1">
+        <v>8</v>
+      </c>
+      <c r="G653" s="1">
+        <v>1</v>
+      </c>
+      <c r="H653" s="1">
+        <v>0</v>
+      </c>
+      <c r="I653" s="2"/>
+      <c r="J653" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="654" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A654" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C654" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D654" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E654" s="1">
+        <v>7</v>
+      </c>
+      <c r="F654" s="1">
+        <v>3</v>
+      </c>
+      <c r="G654" s="1">
+        <v>2</v>
+      </c>
+      <c r="H654" s="1">
+        <v>2</v>
+      </c>
+      <c r="I654" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J654" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="655" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A655" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C655" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D655" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E655" s="1">
+        <v>3</v>
+      </c>
+      <c r="F655" s="1">
+        <v>6</v>
+      </c>
+      <c r="G655" s="1">
+        <v>6</v>
+      </c>
+      <c r="H655" s="1">
+        <v>5</v>
+      </c>
+      <c r="I655" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J655" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="656" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A656" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C656" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D656" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E656" s="1">
+        <v>8</v>
+      </c>
+      <c r="F656" s="1">
+        <v>1</v>
+      </c>
+      <c r="G656" s="1">
+        <v>0</v>
+      </c>
+      <c r="H656" s="1">
+        <v>1</v>
+      </c>
+      <c r="I656" s="2"/>
+      <c r="J656" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="657" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A657" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C657" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D657" s="1">
+        <v>9</v>
+      </c>
+      <c r="E657" s="1">
+        <v>8</v>
+      </c>
+      <c r="F657" s="1">
+        <v>2</v>
+      </c>
+      <c r="G657" s="1">
+        <v>0</v>
+      </c>
+      <c r="H657" s="1">
+        <v>0</v>
+      </c>
+      <c r="I657" s="2"/>
+      <c r="J657" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="658" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A658" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C658" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D658" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E658" s="1">
+        <v>7</v>
+      </c>
+      <c r="F658" s="1">
+        <v>0</v>
+      </c>
+      <c r="G658" s="1">
+        <v>0</v>
+      </c>
+      <c r="H658" s="1">
+        <v>0</v>
+      </c>
+      <c r="I658" s="2"/>
+      <c r="J658" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="659" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A659" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C659" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D659" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E659" s="1">
+        <v>6</v>
+      </c>
+      <c r="F659" s="1">
+        <v>4</v>
+      </c>
+      <c r="G659" s="1">
+        <v>2</v>
+      </c>
+      <c r="H659" s="1">
+        <v>0</v>
+      </c>
+      <c r="I659" s="2"/>
+      <c r="J659" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="660" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A660" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C660" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D660" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E660" s="1">
+        <v>5</v>
+      </c>
+      <c r="F660" s="1">
+        <v>6</v>
+      </c>
+      <c r="G660" s="1">
+        <v>5</v>
+      </c>
+      <c r="H660" s="1">
+        <v>5</v>
+      </c>
+      <c r="I660" s="2"/>
+      <c r="J660" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="661" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A661" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C661" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D661" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E661" s="1">
+        <v>8</v>
+      </c>
+      <c r="F661" s="1">
+        <v>3</v>
+      </c>
+      <c r="G661" s="1">
+        <v>4</v>
+      </c>
+      <c r="H661" s="1">
+        <v>0</v>
+      </c>
+      <c r="I661" s="2"/>
+      <c r="J661" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="662" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A662" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C662" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D662" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E662" s="1">
+        <v>7</v>
+      </c>
+      <c r="F662" s="1">
+        <v>7</v>
+      </c>
+      <c r="G662" s="1">
+        <v>0</v>
+      </c>
+      <c r="H662" s="1">
+        <v>0</v>
+      </c>
+      <c r="I662" s="2"/>
+      <c r="J662" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="663" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A663" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C663" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D663" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E663" s="1">
+        <v>8</v>
+      </c>
+      <c r="F663" s="1">
+        <v>4</v>
+      </c>
+      <c r="G663" s="1">
+        <v>0</v>
+      </c>
+      <c r="H663" s="1">
+        <v>0</v>
+      </c>
+      <c r="I663" s="2"/>
+      <c r="J663" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="664" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A664" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C664" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D664" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E664" s="1">
+        <v>5</v>
+      </c>
+      <c r="F664" s="1">
+        <v>5</v>
+      </c>
+      <c r="G664" s="1">
+        <v>1</v>
+      </c>
+      <c r="H664" s="1">
+        <v>1</v>
+      </c>
+      <c r="I664" s="2"/>
+      <c r="J664" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="665" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A665" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C665" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D665" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E665" s="1">
+        <v>5</v>
+      </c>
+      <c r="F665" s="1">
+        <v>5</v>
+      </c>
+      <c r="G665" s="1">
+        <v>4</v>
+      </c>
+      <c r="H665" s="1">
+        <v>4</v>
+      </c>
+      <c r="I665" s="2"/>
+      <c r="J665" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="666" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A666" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C666" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D666" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E666" s="1">
+        <v>9</v>
+      </c>
+      <c r="F666" s="1">
+        <v>1</v>
+      </c>
+      <c r="G666" s="1">
+        <v>1</v>
+      </c>
+      <c r="H666" s="1">
+        <v>0</v>
+      </c>
+      <c r="I666" s="2"/>
+      <c r="J666" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="667" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A667" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C667" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D667" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E667" s="1">
+        <v>10</v>
+      </c>
+      <c r="F667" s="1">
+        <v>3</v>
+      </c>
+      <c r="G667" s="1">
+        <v>0</v>
+      </c>
+      <c r="H667" s="1">
+        <v>0</v>
+      </c>
+      <c r="I667" s="2"/>
+      <c r="J667" s="1">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/2026-2027/Pré-séance.xlsx
+++ b/data/2026-2027/Pré-séance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDB542D-8501-4945-8BD2-F97234F81AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740116D1-372D-494E-8766-E4FE894C1637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{1A9C3045-D9B1-2C40-BB1C-55E131BFBA85}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="154">
   <si>
     <t>Nom du joueur</t>
   </si>
@@ -480,6 +480,24 @@
   <si>
     <t>8h2</t>
   </si>
+  <si>
+    <t>9h15</t>
+  </si>
+  <si>
+    <t>Quadriceps et mollet </t>
+  </si>
+  <si>
+    <t>Béquilles </t>
+  </si>
+  <si>
+    <t>9h 15</t>
+  </si>
+  <si>
+    <t>Psoas gauche </t>
+  </si>
+  <si>
+    <t>Hanche</t>
+  </si>
 </sst>
 </file>
 
@@ -874,7 +892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D0374B-10DC-0242-BBAD-60229EC6B28B}">
-  <dimension ref="A1:T667"/>
+  <dimension ref="A1:T732"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -21266,6 +21284,1990 @@
         <v>6</v>
       </c>
     </row>
+    <row r="668" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A668" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C668" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D668" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E668" s="1">
+        <v>7</v>
+      </c>
+      <c r="F668" s="1">
+        <v>3</v>
+      </c>
+      <c r="G668" s="1">
+        <v>0</v>
+      </c>
+      <c r="H668" s="1">
+        <v>0</v>
+      </c>
+      <c r="I668" s="2"/>
+      <c r="J668" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="669" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A669" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C669" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D669" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E669" s="1">
+        <v>8</v>
+      </c>
+      <c r="F669" s="1">
+        <v>5</v>
+      </c>
+      <c r="G669" s="1">
+        <v>3</v>
+      </c>
+      <c r="H669" s="1">
+        <v>0</v>
+      </c>
+      <c r="I669" s="2"/>
+      <c r="J669" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="670" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A670" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C670" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D670" s="1">
+        <v>9</v>
+      </c>
+      <c r="E670" s="1">
+        <v>6</v>
+      </c>
+      <c r="F670" s="1">
+        <v>3</v>
+      </c>
+      <c r="G670" s="1">
+        <v>0</v>
+      </c>
+      <c r="H670" s="1">
+        <v>0</v>
+      </c>
+      <c r="I670" s="2"/>
+      <c r="J670" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="671" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A671" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C671" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D671" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E671" s="1">
+        <v>6</v>
+      </c>
+      <c r="F671" s="1">
+        <v>3</v>
+      </c>
+      <c r="G671" s="1">
+        <v>1</v>
+      </c>
+      <c r="H671" s="1">
+        <v>1</v>
+      </c>
+      <c r="I671" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J671" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="672" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A672" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C672" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D672" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E672" s="1">
+        <v>7</v>
+      </c>
+      <c r="F672" s="1">
+        <v>6</v>
+      </c>
+      <c r="G672" s="1">
+        <v>6</v>
+      </c>
+      <c r="H672" s="1">
+        <v>5</v>
+      </c>
+      <c r="I672" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J672" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="673" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A673" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C673" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D673" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E673" s="1">
+        <v>8</v>
+      </c>
+      <c r="F673" s="1">
+        <v>5</v>
+      </c>
+      <c r="G673" s="1">
+        <v>1</v>
+      </c>
+      <c r="H673" s="1">
+        <v>2</v>
+      </c>
+      <c r="I673" s="2"/>
+      <c r="J673" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="674" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A674" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C674" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D674" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E674" s="1">
+        <v>3</v>
+      </c>
+      <c r="F674" s="1">
+        <v>6</v>
+      </c>
+      <c r="G674" s="1">
+        <v>0</v>
+      </c>
+      <c r="H674" s="1">
+        <v>0</v>
+      </c>
+      <c r="I674" s="2"/>
+      <c r="J674" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="675" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A675" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C675" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D675" s="1">
+        <v>9</v>
+      </c>
+      <c r="E675" s="1">
+        <v>8</v>
+      </c>
+      <c r="F675" s="1">
+        <v>2</v>
+      </c>
+      <c r="G675" s="1">
+        <v>4</v>
+      </c>
+      <c r="H675" s="1">
+        <v>0</v>
+      </c>
+      <c r="I675" s="2"/>
+      <c r="J675" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="676" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A676" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C676" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D676" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E676" s="1">
+        <v>6</v>
+      </c>
+      <c r="F676" s="1">
+        <v>0</v>
+      </c>
+      <c r="G676" s="1">
+        <v>0</v>
+      </c>
+      <c r="H676" s="1">
+        <v>0</v>
+      </c>
+      <c r="I676" s="2"/>
+      <c r="J676" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="677" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A677" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C677" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D677" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E677" s="1">
+        <v>5</v>
+      </c>
+      <c r="F677" s="1">
+        <v>5</v>
+      </c>
+      <c r="G677" s="1">
+        <v>4</v>
+      </c>
+      <c r="H677" s="1">
+        <v>4</v>
+      </c>
+      <c r="I677" s="2"/>
+      <c r="J677" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="678" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A678" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C678" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D678" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E678" s="1">
+        <v>8</v>
+      </c>
+      <c r="F678" s="1">
+        <v>3</v>
+      </c>
+      <c r="G678" s="1">
+        <v>0</v>
+      </c>
+      <c r="H678" s="1">
+        <v>0</v>
+      </c>
+      <c r="I678" s="2"/>
+      <c r="J678" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="679" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A679" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C679" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D679" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E679" s="1">
+        <v>6</v>
+      </c>
+      <c r="F679" s="1">
+        <v>5</v>
+      </c>
+      <c r="G679" s="1">
+        <v>6</v>
+      </c>
+      <c r="H679" s="1">
+        <v>5</v>
+      </c>
+      <c r="I679" s="2"/>
+      <c r="J679" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="680" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A680" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C680" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D680" s="5">
+        <v>0.40625</v>
+      </c>
+      <c r="E680" s="1">
+        <v>8</v>
+      </c>
+      <c r="F680" s="1">
+        <v>2</v>
+      </c>
+      <c r="G680" s="1">
+        <v>0</v>
+      </c>
+      <c r="H680" s="1">
+        <v>2</v>
+      </c>
+      <c r="I680" s="2"/>
+      <c r="J680" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="681" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A681" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C681" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D681" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E681" s="1">
+        <v>9</v>
+      </c>
+      <c r="F681" s="1">
+        <v>2</v>
+      </c>
+      <c r="G681" s="1">
+        <v>3</v>
+      </c>
+      <c r="H681" s="1">
+        <v>0</v>
+      </c>
+      <c r="I681" s="2"/>
+      <c r="J681" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="682" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A682" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C682" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D682" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E682" s="1">
+        <v>8</v>
+      </c>
+      <c r="F682" s="1">
+        <v>7</v>
+      </c>
+      <c r="G682" s="1">
+        <v>0</v>
+      </c>
+      <c r="H682" s="1">
+        <v>5</v>
+      </c>
+      <c r="I682" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J682" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="683" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A683" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C683" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D683" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E683" s="1">
+        <v>8</v>
+      </c>
+      <c r="F683" s="1">
+        <v>3</v>
+      </c>
+      <c r="G683" s="1">
+        <v>0</v>
+      </c>
+      <c r="H683" s="1">
+        <v>2</v>
+      </c>
+      <c r="I683" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J683" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="684" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A684" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C684" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D684" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E684" s="1">
+        <v>6</v>
+      </c>
+      <c r="F684" s="1">
+        <v>7</v>
+      </c>
+      <c r="G684" s="1">
+        <v>0</v>
+      </c>
+      <c r="H684" s="1">
+        <v>0</v>
+      </c>
+      <c r="I684" s="2"/>
+      <c r="J684" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="685" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A685" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C685" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D685" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E685" s="1">
+        <v>6</v>
+      </c>
+      <c r="F685" s="1">
+        <v>4</v>
+      </c>
+      <c r="G685" s="1">
+        <v>3</v>
+      </c>
+      <c r="H685" s="1">
+        <v>0</v>
+      </c>
+      <c r="I685" s="2"/>
+      <c r="J685" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="686" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A686" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C686" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D686" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E686" s="1">
+        <v>8</v>
+      </c>
+      <c r="F686" s="1">
+        <v>3</v>
+      </c>
+      <c r="G686" s="1">
+        <v>2</v>
+      </c>
+      <c r="H686" s="1">
+        <v>0</v>
+      </c>
+      <c r="I686" s="2"/>
+      <c r="J686" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="687" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A687" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C687" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D687" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E687" s="1">
+        <v>8</v>
+      </c>
+      <c r="F687" s="1">
+        <v>0</v>
+      </c>
+      <c r="G687" s="1">
+        <v>0</v>
+      </c>
+      <c r="H687" s="1">
+        <v>0</v>
+      </c>
+      <c r="I687" s="2"/>
+      <c r="J687" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="688" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A688" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C688" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D688" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E688" s="1">
+        <v>5</v>
+      </c>
+      <c r="F688" s="1">
+        <v>7</v>
+      </c>
+      <c r="G688" s="1">
+        <v>6</v>
+      </c>
+      <c r="H688" s="1">
+        <v>6</v>
+      </c>
+      <c r="I688" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J688" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="689" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A689" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C689" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D689" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E689" s="1">
+        <v>10</v>
+      </c>
+      <c r="F689" s="1">
+        <v>1</v>
+      </c>
+      <c r="G689" s="1">
+        <v>0</v>
+      </c>
+      <c r="H689" s="1">
+        <v>0</v>
+      </c>
+      <c r="I689" s="2"/>
+      <c r="J689" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="690" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A690" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C690" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D690" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E690" s="1">
+        <v>7</v>
+      </c>
+      <c r="F690" s="1">
+        <v>3</v>
+      </c>
+      <c r="G690" s="1">
+        <v>0</v>
+      </c>
+      <c r="H690" s="1">
+        <v>0</v>
+      </c>
+      <c r="I690" s="2"/>
+      <c r="J690" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="691" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A691" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C691" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D691" s="1">
+        <v>8</v>
+      </c>
+      <c r="E691" s="1">
+        <v>6</v>
+      </c>
+      <c r="F691" s="1">
+        <v>3</v>
+      </c>
+      <c r="G691" s="1">
+        <v>2</v>
+      </c>
+      <c r="H691" s="1">
+        <v>1</v>
+      </c>
+      <c r="I691" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J691" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="692" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A692" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C692" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D692" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E692" s="1">
+        <v>6</v>
+      </c>
+      <c r="F692" s="1">
+        <v>7</v>
+      </c>
+      <c r="G692" s="1">
+        <v>0</v>
+      </c>
+      <c r="H692" s="1">
+        <v>0</v>
+      </c>
+      <c r="I692" s="2"/>
+      <c r="J692" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="693" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A693" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C693" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D693" s="1">
+        <v>9</v>
+      </c>
+      <c r="E693" s="1">
+        <v>7</v>
+      </c>
+      <c r="F693" s="1">
+        <v>1</v>
+      </c>
+      <c r="G693" s="1">
+        <v>1</v>
+      </c>
+      <c r="H693" s="1">
+        <v>7</v>
+      </c>
+      <c r="I693" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J693" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="694" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A694" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C694" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D694" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E694" s="1">
+        <v>6</v>
+      </c>
+      <c r="F694" s="1">
+        <v>4</v>
+      </c>
+      <c r="G694" s="1">
+        <v>2</v>
+      </c>
+      <c r="H694" s="1">
+        <v>0</v>
+      </c>
+      <c r="I694" s="2"/>
+      <c r="J694" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="695" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A695" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C695" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D695" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E695" s="1">
+        <v>8</v>
+      </c>
+      <c r="F695" s="1">
+        <v>3</v>
+      </c>
+      <c r="G695" s="1">
+        <v>0</v>
+      </c>
+      <c r="H695" s="1">
+        <v>0</v>
+      </c>
+      <c r="I695" s="2"/>
+      <c r="J695" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="696" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A696" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C696" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D696" s="1">
+        <v>9</v>
+      </c>
+      <c r="E696" s="1">
+        <v>8</v>
+      </c>
+      <c r="F696" s="1">
+        <v>2</v>
+      </c>
+      <c r="G696" s="1">
+        <v>0</v>
+      </c>
+      <c r="H696" s="1">
+        <v>0</v>
+      </c>
+      <c r="I696" s="2"/>
+      <c r="J696" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="697" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A697" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D697" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E697" s="1">
+        <v>6</v>
+      </c>
+      <c r="F697" s="1">
+        <v>5</v>
+      </c>
+      <c r="G697" s="1">
+        <v>1</v>
+      </c>
+      <c r="H697" s="1">
+        <v>4</v>
+      </c>
+      <c r="I697" s="2"/>
+      <c r="J697" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="698" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A698" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C698" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D698" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E698" s="1">
+        <v>8</v>
+      </c>
+      <c r="F698" s="1">
+        <v>2</v>
+      </c>
+      <c r="G698" s="1">
+        <v>2</v>
+      </c>
+      <c r="H698" s="1">
+        <v>0</v>
+      </c>
+      <c r="I698" s="2"/>
+      <c r="J698" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="699" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A699" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D699" s="1">
+        <v>7</v>
+      </c>
+      <c r="E699" s="1">
+        <v>6</v>
+      </c>
+      <c r="F699" s="1">
+        <v>6</v>
+      </c>
+      <c r="G699" s="1">
+        <v>0</v>
+      </c>
+      <c r="H699" s="1">
+        <v>2</v>
+      </c>
+      <c r="I699" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J699" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="700" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A700" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C700" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D700" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E700" s="1">
+        <v>6</v>
+      </c>
+      <c r="F700" s="1">
+        <v>6</v>
+      </c>
+      <c r="G700" s="1">
+        <v>0</v>
+      </c>
+      <c r="H700" s="1">
+        <v>0</v>
+      </c>
+      <c r="I700" s="2"/>
+      <c r="J700" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="701" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A701" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C701" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D701" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E701" s="1">
+        <v>6</v>
+      </c>
+      <c r="F701" s="1">
+        <v>3</v>
+      </c>
+      <c r="G701" s="1">
+        <v>6</v>
+      </c>
+      <c r="H701" s="1">
+        <v>4</v>
+      </c>
+      <c r="I701" s="2"/>
+      <c r="J701" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="702" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A702" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C702" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D702" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E702" s="1">
+        <v>8</v>
+      </c>
+      <c r="F702" s="1">
+        <v>0</v>
+      </c>
+      <c r="G702" s="1">
+        <v>0</v>
+      </c>
+      <c r="H702" s="1">
+        <v>0</v>
+      </c>
+      <c r="I702" s="2"/>
+      <c r="J702" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="703" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A703" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C703" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D703" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E703" s="1">
+        <v>6</v>
+      </c>
+      <c r="F703" s="1">
+        <v>4</v>
+      </c>
+      <c r="G703" s="1">
+        <v>0</v>
+      </c>
+      <c r="H703" s="1">
+        <v>0</v>
+      </c>
+      <c r="I703" s="2"/>
+      <c r="J703" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="704" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A704" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C704" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D704" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E704" s="1">
+        <v>7</v>
+      </c>
+      <c r="F704" s="1">
+        <v>4</v>
+      </c>
+      <c r="G704" s="1">
+        <v>1</v>
+      </c>
+      <c r="H704" s="1">
+        <v>2</v>
+      </c>
+      <c r="I704" s="2"/>
+      <c r="J704" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="705" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A705" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B705" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C705" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D705" s="1">
+        <v>9</v>
+      </c>
+      <c r="E705" s="1">
+        <v>8</v>
+      </c>
+      <c r="F705" s="1">
+        <v>2</v>
+      </c>
+      <c r="G705" s="1">
+        <v>0</v>
+      </c>
+      <c r="H705" s="1">
+        <v>0</v>
+      </c>
+      <c r="I705" s="2"/>
+      <c r="J705" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="706" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A706" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B706" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C706" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D706" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E706" s="1">
+        <v>5</v>
+      </c>
+      <c r="F706" s="1">
+        <v>6</v>
+      </c>
+      <c r="G706" s="1">
+        <v>5</v>
+      </c>
+      <c r="H706" s="1">
+        <v>5</v>
+      </c>
+      <c r="I706" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J706" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="707" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A707" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B707" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C707" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D707" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E707" s="1">
+        <v>8</v>
+      </c>
+      <c r="F707" s="1">
+        <v>2</v>
+      </c>
+      <c r="G707" s="1">
+        <v>0</v>
+      </c>
+      <c r="H707" s="1">
+        <v>2</v>
+      </c>
+      <c r="I707" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J707" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="708" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A708" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B708" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C708" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D708" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E708" s="1">
+        <v>5</v>
+      </c>
+      <c r="F708" s="1">
+        <v>6</v>
+      </c>
+      <c r="G708" s="1">
+        <v>4</v>
+      </c>
+      <c r="H708" s="1">
+        <v>4</v>
+      </c>
+      <c r="I708" s="2"/>
+      <c r="J708" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="709" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A709" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B709" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C709" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D709" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E709" s="1">
+        <v>5</v>
+      </c>
+      <c r="F709" s="1">
+        <v>4</v>
+      </c>
+      <c r="G709" s="1">
+        <v>0</v>
+      </c>
+      <c r="H709" s="1">
+        <v>0</v>
+      </c>
+      <c r="I709" s="2"/>
+      <c r="J709" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="710" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A710" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B710" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C710" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D710" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E710" s="1">
+        <v>7</v>
+      </c>
+      <c r="F710" s="1">
+        <v>3</v>
+      </c>
+      <c r="G710" s="1">
+        <v>4</v>
+      </c>
+      <c r="H710" s="1">
+        <v>0</v>
+      </c>
+      <c r="I710" s="2"/>
+      <c r="J710" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="711" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A711" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C711" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D711" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E711" s="1">
+        <v>7</v>
+      </c>
+      <c r="F711" s="1">
+        <v>4</v>
+      </c>
+      <c r="G711" s="1">
+        <v>1</v>
+      </c>
+      <c r="H711" s="1">
+        <v>0</v>
+      </c>
+      <c r="I711" s="2"/>
+      <c r="J711" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="712" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A712" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B712" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C712" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D712" s="1">
+        <v>9</v>
+      </c>
+      <c r="E712" s="1">
+        <v>8</v>
+      </c>
+      <c r="F712" s="1">
+        <v>2</v>
+      </c>
+      <c r="G712" s="1">
+        <v>0</v>
+      </c>
+      <c r="H712" s="1">
+        <v>6</v>
+      </c>
+      <c r="I712" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J712" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="713" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A713" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B713" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C713" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D713" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E713" s="1">
+        <v>10</v>
+      </c>
+      <c r="F713" s="1">
+        <v>0</v>
+      </c>
+      <c r="G713" s="1">
+        <v>0</v>
+      </c>
+      <c r="H713" s="1">
+        <v>0</v>
+      </c>
+      <c r="I713" s="2"/>
+      <c r="J713" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="714" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A714" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C714" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D714" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E714" s="1">
+        <v>8</v>
+      </c>
+      <c r="F714" s="1">
+        <v>0</v>
+      </c>
+      <c r="G714" s="1">
+        <v>0</v>
+      </c>
+      <c r="H714" s="1">
+        <v>0</v>
+      </c>
+      <c r="I714" s="2"/>
+      <c r="J714" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="715" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A715" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B715" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C715" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D715" s="1">
+        <v>8</v>
+      </c>
+      <c r="E715" s="1">
+        <v>7</v>
+      </c>
+      <c r="F715" s="1">
+        <v>8</v>
+      </c>
+      <c r="G715" s="1">
+        <v>0</v>
+      </c>
+      <c r="H715" s="1">
+        <v>0</v>
+      </c>
+      <c r="I715" s="2"/>
+      <c r="J715" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="716" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A716" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B716" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C716" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D716" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E716" s="1">
+        <v>5</v>
+      </c>
+      <c r="F716" s="1">
+        <v>5</v>
+      </c>
+      <c r="G716" s="1">
+        <v>0</v>
+      </c>
+      <c r="H716" s="1">
+        <v>3</v>
+      </c>
+      <c r="I716" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J716" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="717" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A717" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B717" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C717" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D717" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E717" s="1">
+        <v>6</v>
+      </c>
+      <c r="F717" s="1">
+        <v>3</v>
+      </c>
+      <c r="G717" s="1">
+        <v>2</v>
+      </c>
+      <c r="H717" s="1">
+        <v>1</v>
+      </c>
+      <c r="I717" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J717" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="718" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A718" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B718" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C718" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D718" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E718" s="1">
+        <v>5</v>
+      </c>
+      <c r="F718" s="1">
+        <v>7</v>
+      </c>
+      <c r="G718" s="1">
+        <v>0</v>
+      </c>
+      <c r="H718" s="1">
+        <v>0</v>
+      </c>
+      <c r="I718" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J718" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="719" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A719" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B719" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C719" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D719" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E719" s="1">
+        <v>8</v>
+      </c>
+      <c r="F719" s="1">
+        <v>3</v>
+      </c>
+      <c r="G719" s="1">
+        <v>4</v>
+      </c>
+      <c r="H719" s="1">
+        <v>0</v>
+      </c>
+      <c r="I719" s="2"/>
+      <c r="J719" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="720" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A720" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B720" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C720" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D720" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E720" s="1">
+        <v>7</v>
+      </c>
+      <c r="F720" s="1">
+        <v>4</v>
+      </c>
+      <c r="G720" s="1">
+        <v>0</v>
+      </c>
+      <c r="H720" s="1">
+        <v>0</v>
+      </c>
+      <c r="I720" s="2"/>
+      <c r="J720" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="721" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A721" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B721" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C721" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D721" s="5">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="E721" s="1">
+        <v>5</v>
+      </c>
+      <c r="F721" s="1">
+        <v>4</v>
+      </c>
+      <c r="G721" s="1">
+        <v>0</v>
+      </c>
+      <c r="H721" s="1">
+        <v>0</v>
+      </c>
+      <c r="I721" s="2"/>
+      <c r="J721" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="722" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A722" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B722" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C722" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D722" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E722" s="1">
+        <v>7</v>
+      </c>
+      <c r="F722" s="1">
+        <v>4</v>
+      </c>
+      <c r="G722" s="1">
+        <v>0</v>
+      </c>
+      <c r="H722" s="1">
+        <v>0</v>
+      </c>
+      <c r="I722" s="2"/>
+      <c r="J722" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="723" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A723" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B723" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C723" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D723" s="1">
+        <v>9</v>
+      </c>
+      <c r="E723" s="1">
+        <v>8</v>
+      </c>
+      <c r="F723" s="1">
+        <v>5</v>
+      </c>
+      <c r="G723" s="1">
+        <v>0</v>
+      </c>
+      <c r="H723" s="1">
+        <v>0</v>
+      </c>
+      <c r="I723" s="2"/>
+      <c r="J723" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="724" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A724" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B724" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C724" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D724" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E724" s="1">
+        <v>8</v>
+      </c>
+      <c r="F724" s="1">
+        <v>3</v>
+      </c>
+      <c r="G724" s="1">
+        <v>0</v>
+      </c>
+      <c r="H724" s="1">
+        <v>3</v>
+      </c>
+      <c r="I724" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J724" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="725" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A725" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B725" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C725" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D725" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E725" s="1">
+        <v>7</v>
+      </c>
+      <c r="F725" s="1">
+        <v>3</v>
+      </c>
+      <c r="G725" s="1">
+        <v>0</v>
+      </c>
+      <c r="H725" s="1">
+        <v>0</v>
+      </c>
+      <c r="I725" s="2"/>
+      <c r="J725" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="726" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A726" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B726" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C726" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D726" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E726" s="1">
+        <v>5</v>
+      </c>
+      <c r="F726" s="1">
+        <v>6</v>
+      </c>
+      <c r="G726" s="1">
+        <v>6</v>
+      </c>
+      <c r="H726" s="1">
+        <v>6</v>
+      </c>
+      <c r="I726" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J726" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="727" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A727" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B727" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C727" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D727" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E727" s="1">
+        <v>7</v>
+      </c>
+      <c r="F727" s="1">
+        <v>4</v>
+      </c>
+      <c r="G727" s="1">
+        <v>3</v>
+      </c>
+      <c r="H727" s="1">
+        <v>0</v>
+      </c>
+      <c r="I727" s="2"/>
+      <c r="J727" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="728" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A728" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B728" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C728" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D728" s="1">
+        <v>9</v>
+      </c>
+      <c r="E728" s="1">
+        <v>7</v>
+      </c>
+      <c r="F728" s="1">
+        <v>2</v>
+      </c>
+      <c r="G728" s="1">
+        <v>3</v>
+      </c>
+      <c r="H728" s="1">
+        <v>4</v>
+      </c>
+      <c r="I728" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J728" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="729" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A729" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B729" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C729" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D729" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E729" s="1">
+        <v>8</v>
+      </c>
+      <c r="F729" s="1">
+        <v>0</v>
+      </c>
+      <c r="G729" s="1">
+        <v>0</v>
+      </c>
+      <c r="H729" s="1">
+        <v>0</v>
+      </c>
+      <c r="I729" s="2"/>
+      <c r="J729" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="730" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A730" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C730" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D730" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E730" s="1">
+        <v>6</v>
+      </c>
+      <c r="F730" s="1">
+        <v>5</v>
+      </c>
+      <c r="G730" s="1">
+        <v>6</v>
+      </c>
+      <c r="H730" s="1">
+        <v>3</v>
+      </c>
+      <c r="I730" s="2"/>
+      <c r="J730" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="731" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A731" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C731" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D731" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E731" s="1">
+        <v>5</v>
+      </c>
+      <c r="F731" s="1">
+        <v>4</v>
+      </c>
+      <c r="G731" s="1">
+        <v>4</v>
+      </c>
+      <c r="H731" s="1">
+        <v>4</v>
+      </c>
+      <c r="I731" s="2"/>
+      <c r="J731" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="732" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A732" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C732" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D732" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E732" s="1">
+        <v>7</v>
+      </c>
+      <c r="F732" s="1">
+        <v>5</v>
+      </c>
+      <c r="G732" s="1">
+        <v>0</v>
+      </c>
+      <c r="H732" s="1">
+        <v>0</v>
+      </c>
+      <c r="I732" s="2"/>
+      <c r="J732" s="1">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
